--- a/Employee_Reports_wi52/Edison Mendoza Rojas Q0505.xlsx
+++ b/Employee_Reports_wi52/Edison Mendoza Rojas Q0505.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1206,11 +1206,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1304,11 +1304,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1353,11 +1353,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1402,11 +1402,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1451,11 +1451,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1500,11 +1500,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1549,11 +1549,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1598,11 +1598,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1647,11 +1647,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1696,11 +1696,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1745,11 +1745,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1794,11 +1794,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1831,11 +1831,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1880,11 +1880,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1929,11 +1929,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1979,11 +1979,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -2028,11 +2028,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2065,11 +2065,11 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2114,11 +2114,11 @@
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-151</v>
+        <v>-159</v>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2163,11 +2163,11 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2212,11 +2212,11 @@
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-152</v>
+        <v>-160</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2261,11 +2261,11 @@
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-102</v>
+        <v>-110</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -2310,11 +2310,11 @@
         </is>
       </c>
       <c r="H39" s="3" t="n">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -2359,11 +2359,11 @@
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-105</v>
+        <v>-113</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -2408,11 +2408,11 @@
         </is>
       </c>
       <c r="H41" s="3" t="n">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -2445,11 +2445,11 @@
         </is>
       </c>
       <c r="H42" s="3" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -2494,11 +2494,11 @@
         </is>
       </c>
       <c r="H43" s="3" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -2531,11 +2531,11 @@
         </is>
       </c>
       <c r="H44" s="3" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -2568,11 +2568,11 @@
         </is>
       </c>
       <c r="H45" s="3" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -2617,11 +2617,11 @@
         </is>
       </c>
       <c r="H46" s="3" t="n">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -2666,11 +2666,11 @@
         </is>
       </c>
       <c r="H47" s="3" t="n">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -2715,11 +2715,11 @@
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -2752,11 +2752,11 @@
         </is>
       </c>
       <c r="H49" s="3" t="n">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -2789,11 +2789,11 @@
         </is>
       </c>
       <c r="H50" s="3" t="n">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -2826,11 +2826,11 @@
         </is>
       </c>
       <c r="H51" s="3" t="n">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -2863,11 +2863,11 @@
         </is>
       </c>
       <c r="H52" s="3" t="n">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7612</v>
+        <v>7604</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7911</v>
+        <v>7903</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7943</v>
+        <v>7935</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7939</v>
+        <v>7931</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7938</v>
+        <v>7930</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7945</v>
+        <v>7937</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
